--- a/data/2025/06-bistrita-nasaud/32394-bistrita/budget_file.xlsx
+++ b/data/2025/06-bistrita-nasaud/32394-bistrita/budget_file.xlsx
@@ -569,18 +569,12 @@
         <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="4" t="n">
-        <v>169000</v>
-      </c>
+      <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n">
-        <v>210000</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>210000</v>
-      </c>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
@@ -591,7 +585,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>unparseable cell "0,00 00'0" in column trim1; unparseable cell "0,00 00'0" in column trim2</t>
+          <t>unparseable cell '169,00 0,00' in column total_2026; unparseable cell "0,00 00'0" in column trim1; unparseable cell "0,00 00'0" in column trim2; unparseable cell '210,00 0,00' in column trim3; unparseable cell '210,00 0,00' in column trim4</t>
         </is>
       </c>
     </row>
@@ -877,104 +871,104 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>20.30</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>998,00 0,00 1.520,00 20.300+00+.+0.0+0.30.3 Alte cheltuieli (cod 20.30.01 la</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n">
         <v>250</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="M10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2027</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>20.30.01</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>100,00 00'0 357,00 Reclama si publicitate 0</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="M11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '00°0' in column est2028</t>
         </is>
       </c>
     </row>
@@ -1163,104 +1157,104 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>55.01.18</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>448,00 0,00 628,00 55.01.18+55.01.63+55.01.65) Alte transferuri curente interne</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2028</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>55.02</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>3,00 0,00 3,00 B. Transferuri curente in strainatate (catre organizatii internationale) (cod</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2028</t>
         </is>
       </c>
     </row>
@@ -1308,141 +1302,149 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>20,00 0,00 0,00 72,00 TITLJL XI ALTE CHELTUIELI (cod 59.01 + 59.02 + 59.08 +59.11 +59.12 +59.15 +59.17 +59.20+59.22 +59.25 +59.30+59.35)</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '15,00 0,00' in column trim4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>59.01.59.40</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>0,00 20,00 0,00 0,00 000 72,00 Sure oe oeee e sicae Burse</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '0,00 0,00' in column est2027; unparseable cell '0,00 0,00' in column est2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1.835,00 0,00 13.535,00 OPERATIUNI FINANCIARE (cod 80+81) neîncadrate</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n">
+        <v>3900</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>3900</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>3900</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>13510</v>
+      </c>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n">
         <v>15000</v>
       </c>
-      <c r="M19" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="O19" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>59.01.59.40</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>0,00 20,00 0,00 0,00 000 72,00 Sure oe oeee e sicae Burse</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="M20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1.835,00 0,00 13.535,00 OPERATIUNI FINANCIARE (cod 80+81) neîncadrate</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n">
-        <v>3900</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>3900</v>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>3900</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>13510</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>11832</v>
-      </c>
-      <c r="O21" s="6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '0,00 11.832,00' in column est2028</t>
         </is>
       </c>
     </row>
@@ -1484,53 +1486,53 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>81.01</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>0,00 00'0 0,00 81.0..+.+.+.06) Rambursari de credite externe (cod</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2027</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S76"/>
+  <dimension ref="A1:S77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3396,117 +3398,115 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL (cOd 10.01+10.02+10.03)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>16</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>10900</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="6" t="n">
         <v>3167</v>
       </c>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="n">
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="n">
         <v>3373</v>
       </c>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n">
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n">
         <v>11030</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="P14" s="6" t="n">
         <v>11100</v>
       </c>
-      <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>10 trim1: parent 3.373,00 != sum(children) 3.307,00 (2 children); 10 total_2026: parent 3.167,00 != sum(children) 3.102,00 (2 children); 10 total: parent 10.900,00 != sum(children) 10.659,00 (2 children)</t>
+      <c r="Q14" s="6" t="n"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Cheltuieli salariale in bani (cod 11.01+10.01.03 la 10.01.08 +10.01.10 la .1.16 +10.01.30)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>(rând derivat din formula tipărită)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>9464</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>2712</v>
-      </c>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>2942</v>
-      </c>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6" t="n"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>241</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="8" t="n"/>
+      <c r="O15" s="8" t="n">
+        <v>11030</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>11100</v>
+      </c>
+      <c r="Q15" s="8" t="n"/>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>rând absent, derivat aritmetic din formula părintelui 10; name mismatch vs nomenclator (30%): '(rând derivat din formula tipărită)' vs 'Contributii'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.01.01</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salarii de bază</t>
+          <t>Cheltuieli salariale in bani (cod 11.01+10.01.03 la 10.01.08 +10.01.10 la .1.16 +10.01.30)</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -3518,17 +3518,17 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>8875</v>
+        <v>9464</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2535</v>
+        <v>2712</v>
       </c>
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>2750</v>
+        <v>2942</v>
       </c>
       <c r="L16" s="6" t="n"/>
       <c r="M16" s="6" t="n"/>
@@ -3549,12 +3549,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.01.05</t>
+          <t>10.01.01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sporuri pentru conditii de munca</t>
+          <t>Salarii de bază</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -3566,17 +3566,17 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>265</v>
+        <v>8875</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>80</v>
+        <v>2535</v>
       </c>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>80</v>
+        <v>2750</v>
       </c>
       <c r="L17" s="6" t="n"/>
       <c r="M17" s="6" t="n"/>
@@ -3597,12 +3597,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.01.17</t>
+          <t>10.01.05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indemnizații de hrană</t>
+          <t>Sporuri pentru conditii de munca</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -3614,17 +3614,17 @@
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>24</v>
+        <v>265</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="L18" s="6" t="n"/>
       <c r="M18" s="6" t="n"/>
@@ -3645,12 +3645,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.01.30</t>
+          <t>10.01.17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alte drepturi salariale in bani</t>
+          <t>Indemnizații de hrană</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -3662,17 +3662,17 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>300</v>
+        <v>24</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="L19" s="6" t="n"/>
       <c r="M19" s="6" t="n"/>
@@ -3691,117 +3691,117 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10.01.30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Alte drepturi salariale in bani</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6" t="n"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>10.02</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Cheltuieli salariale in natura (cod 10.02.01 la 10.02.06+10.02.30)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n">
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>1195</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>390</v>
       </c>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="4" t="n">
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
         <v>365</v>
       </c>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="4" t="n"/>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>10.02 trim1: parent 365,00 != sum(children) 300,00 (2 children); 10.02 total: parent 1.195,00 != sum(children) 1.130,00 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>10.02.02</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Norme de hrana</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>16</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>925</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>225</v>
-      </c>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n"/>
-      <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="6" t="n"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.02.03</t>
+          <t>10.02.02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uniforme si echipament obligatoriu</t>
+          <t>Norme de hrana</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3813,17 +3813,17 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>205</v>
+        <v>925</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>165</v>
+        <v>225</v>
       </c>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L22" s="6" t="n"/>
       <c r="M22" s="6" t="n"/>
@@ -3842,35 +3842,46 @@
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>PREVEDERI TRIMESTRIALE Trim. I</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>10.02.03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Uniforme si echipament obligatoriu</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" s="6" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>205</v>
+      </c>
       <c r="H23" s="6" t="n">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
+      <c r="J23" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="K23" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>923</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>223</v>
-      </c>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="6" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" s="6" t="n"/>
       <c r="R23" t="inlineStr">
         <is>
@@ -3881,7 +3892,7 @@
     <row r="24">
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>bugetare deslinate din care credite stingerii platilor restante</t>
+          <t>PREVEDERI TRIMESTRIALE Trim. I</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3890,21 +3901,21 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0</v>
+        <v>923</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="O24" s="6" t="n"/>
       <c r="P24" s="6" t="n"/>
@@ -3918,7 +3929,7 @@
     <row r="25">
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>PREVEDERI ANUALE TOTAL</t>
+          <t>bugetare deslinate din care credite stingerii platilor restante</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3927,21 +3938,21 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>1896</v>
+        <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="O25" s="6" t="n"/>
       <c r="P25" s="6" t="n"/>
@@ -3955,7 +3966,7 @@
     <row r="26">
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>indicator Cod Denumirea indicatorilor</t>
+          <t>PREVEDERI ANUALE TOTAL</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3964,21 +3975,21 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="6" t="n">
-        <v>100206</v>
+        <v>65</v>
       </c>
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n">
-        <v>1003</v>
+        <v>241</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>100307</v>
+        <v>241</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>22</v>
+        <v>1896</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2001</v>
+        <v>492</v>
       </c>
       <c r="O26" s="6" t="n"/>
       <c r="P26" s="6" t="n"/>
@@ -3990,44 +4001,35 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20.06.01</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Deplasari interne, detasari, transferari</t>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>indicator Cod Denumirea indicatorilor</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="6" t="n">
-        <v>6</v>
+        <v>100206</v>
       </c>
       <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="6" t="n"/>
-      <c r="M27" s="6" t="n"/>
-      <c r="N27" s="6" t="n"/>
-      <c r="O27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v>0</v>
-      </c>
+        <v>1003</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>100307</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>2001</v>
+      </c>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="n"/>
       <c r="Q27" s="6" t="n"/>
       <c r="R27" t="inlineStr">
         <is>
@@ -4038,12 +4040,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.06.01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pregatire profesionala</t>
+          <t>Deplasari interne, detasari, transferari</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -4056,14 +4058,14 @@
       </c>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L28" s="6" t="n"/>
       <c r="M28" s="6" t="n"/>
@@ -4084,12 +4086,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Protectia muncii</t>
+          <t>Pregatire profesionala</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -4102,7 +4104,7 @@
       </c>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n">
@@ -4130,12 +4132,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alte cheltuieli (cod 20.30.01 la 30.04+20.30.06+20.30.07+20.30.09+20.30.3</t>
+          <t>Protectia muncii</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4148,14 +4150,14 @@
       </c>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="6" t="n">
-        <v>1201</v>
+        <v>60</v>
       </c>
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>589</v>
+        <v>15</v>
       </c>
       <c r="L30" s="6" t="n"/>
       <c r="M30" s="6" t="n"/>
@@ -4176,12 +4178,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20.30.01</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reclama si publicitate</t>
+          <t>Alte cheltuieli (cod 20.30.01 la 30.04+20.30.06+20.30.07+20.30.09+20.30.3</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4194,14 +4196,14 @@
       </c>
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="6" t="n">
-        <v>1</v>
+        <v>1201</v>
       </c>
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>1</v>
+        <v>589</v>
       </c>
       <c r="L31" s="6" t="n"/>
       <c r="M31" s="6" t="n"/>
@@ -4222,12 +4224,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20.30.03</t>
+          <t>20.30.01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prime de asigurare non-viata</t>
+          <t>Reclama si publicitate</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4240,14 +4242,14 @@
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L32" s="6" t="n"/>
       <c r="M32" s="6" t="n"/>
@@ -4268,12 +4270,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20.30.30</t>
+          <t>20.30.03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alte cheltuieli cu bunuri si servicii</t>
+          <t>Prime de asigurare non-viata</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4286,14 +4288,14 @@
       </c>
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="6" t="n">
-        <v>1185</v>
+        <v>15</v>
       </c>
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>585</v>
+        <v>3</v>
       </c>
       <c r="L33" s="6" t="n"/>
       <c r="M33" s="6" t="n"/>
@@ -4314,12 +4316,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20.30.30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TITLUL XI ALTE CHELTUIELI (cOd 59.01 + 59.02 + 59.08 +59.11 +59.12 +59.15 +59.17 +59.20+59.22 +59.25 +59.30+59.35)</t>
+          <t>Alte cheltuieli cu bunuri si servicii</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4332,23 +4334,23 @@
       </c>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n">
-        <v>10</v>
+        <v>1185</v>
       </c>
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>4</v>
+        <v>585</v>
       </c>
       <c r="L34" s="6" t="n"/>
       <c r="M34" s="6" t="n"/>
       <c r="N34" s="6" t="n"/>
       <c r="O34" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="6" t="n"/>
       <c r="R34" t="inlineStr">
@@ -4360,12 +4362,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Burse</t>
+          <t>TITLUL XI ALTE CHELTUIELI (cOd 59.01 + 59.02 + 59.08 +59.11 +59.12 +59.15 +59.17 +59.20+59.22 +59.25 +59.30+59.35)</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4378,23 +4380,23 @@
       </c>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35" s="6" t="n"/>
       <c r="M35" s="6" t="n"/>
       <c r="N35" s="6" t="n"/>
       <c r="O35" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q35" s="6" t="n"/>
       <c r="R35" t="inlineStr">
@@ -4406,12 +4408,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>59.40</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sume aferente persoanelor cu handicap neîncadrate</t>
+          <t>Burse</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4424,14 +4426,14 @@
       </c>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L36" s="6" t="n"/>
       <c r="M36" s="6" t="n"/>
@@ -4450,25 +4452,34 @@
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>SECTIUNEA DE DEZVOLTARE (cod 51+55+56+58+70+79+85)</t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>59.40</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sume aferente persoanelor cu handicap neîncadrate</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>18</v>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
       <c r="G37" s="6" t="n"/>
       <c r="H37" s="6" t="n">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="L37" s="6" t="n"/>
       <c r="M37" s="6" t="n"/>
@@ -4487,24 +4498,15 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CHELTUIELI DE CAPITAL (cod 71+72+75)</t>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>SECTIUNEA DE DEZVOLTARE (cod 51+55+56+58+70+79+85)</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>18</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="6" t="n">
         <v>400</v>
@@ -4535,12 +4537,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TITLUL XV ACTIVE NEFINANCIARE (cOd 71.01 + 71.03)</t>
+          <t>CHELTUIELI DE CAPITAL (cod 71+72+75)</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4581,12 +4583,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Active fixe (cod 71.01.01 la 71.01.03+71.01.30)</t>
+          <t>TITLUL XV ACTIVE NEFINANCIARE (cOd 71.01 + 71.03)</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4627,12 +4629,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>71.01.02</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ini, echipamente si mijloace de transport</t>
+          <t>Active fixe (cod 71.01.01 la 71.01.03+71.01.30)</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4673,16 +4675,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20.30.03</t>
+          <t>71.01.02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prime de asigurare non-viata</t>
+          <t>ini, echipamente si mijloace de transport</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4691,14 +4693,14 @@
       </c>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>3</v>
+        <v>400</v>
       </c>
       <c r="L42" s="6" t="n"/>
       <c r="M42" s="6" t="n"/>
@@ -4712,19 +4714,19 @@
       <c r="Q42" s="6" t="n"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20.30.30</t>
+          <t>20.30.03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alte cheltuieli cu bunuri si servicii</t>
+          <t>Prime de asigurare non-viata</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4737,14 +4739,14 @@
       </c>
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I43" s="6" t="n"/>
       <c r="J43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="L43" s="6" t="n"/>
       <c r="M43" s="6" t="n"/>
@@ -4758,65 +4760,62 @@
       <c r="Q43" s="6" t="n"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>5,00 Trim. II bugetare destinate 0,00 stingerii platilor restante TOTAL indicatorilor</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n"/>
-      <c r="M44" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>unparseable cell 'Trim.1' in column credite_stinse</t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20.30.30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Alte cheltuieli cu bunuri si servicii</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>21</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
+      <c r="N44" s="6" t="n"/>
+      <c r="O44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="6" t="n"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>10.03.07.20</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>525,00 0,00 21,00 1.496,00 TITLUL II BUNURI SI SERVICII (cod 20.01 la Couine  atea aiunca 20.06+20.09 la 20.16+20.18 la</t>
+          <t>5,00 Trim. II bugetare destinate 0,00 stingerii platilor restante TOTAL indicatorilor</t>
         </is>
       </c>
       <c r="D45" s="2" t="n"/>
@@ -4831,88 +4830,89 @@
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell 'Trim.1' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>10.03.07.20</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>525,00 0,00 21,00 1.496,00 TITLUL II BUNURI SI SERVICII (cod 20.01 la Couine  atea aiunca 20.06+20.09 la 20.16+20.18 la</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n">
         <v>198</v>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N46" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="O45" s="4" t="n">
+      <c r="O46" s="4" t="n">
         <v>1550</v>
       </c>
-      <c r="P45" s="4" t="n">
+      <c r="P46" s="4" t="n">
         <v>1600</v>
       </c>
-      <c r="Q45" s="4" t="n">
+      <c r="Q46" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>unparseable cell '6,00 726,00' in column credite_stinse</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>77,00 0,00 231,00 Bunuri si servicii(cod 20.01.01 la 20.25+20.27+20.30)</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>23</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
-      <c r="I46" s="6" t="n">
-        <v>92</v>
-      </c>
-      <c r="J46" s="6" t="n"/>
-      <c r="K46" s="6" t="n"/>
-      <c r="L46" s="6" t="n"/>
-      <c r="M46" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="N46" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="O46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20.01.01</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2,00 8,00 20.01.09+20.01.30) F.íturi de birou</t>
+          <t>77,00 0,00 231,00 Bunuri si servicii(cod 20.01.01 la 20.25+20.27+20.30)</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -4926,483 +4926,514 @@
       <c r="G47" s="6" t="n"/>
       <c r="H47" s="6" t="n"/>
       <c r="I47" s="6" t="n">
-        <v>3000</v>
+        <v>92</v>
       </c>
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
       <c r="L47" s="6" t="n"/>
       <c r="M47" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="N47" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>20.01.01</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2,00 8,00 20.01.09+20.01.30) F.íturi de birou</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N47" s="6" t="n">
+      <c r="N48" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="O48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '3,00 0,00' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>20.01.02</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>0,00 3,00 Materiale pentru curatenie</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
-      <c r="I48" s="6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J48" s="6" t="n"/>
-      <c r="K48" s="6" t="n"/>
-      <c r="L48" s="6" t="n"/>
-      <c r="M48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '3,00 0,00' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>20.01.03</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>15,00 45,00 Încalzit, fluminat si forta motrica</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
-      <c r="I49" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J49" s="6" t="n"/>
-      <c r="K49" s="6" t="n"/>
-      <c r="L49" s="6" t="n"/>
-      <c r="M49" s="6" t="n">
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="N49" s="6" t="n">
+      <c r="N50" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="O50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '20,00 0,00' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>20.01.04</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>2,00 5,00 Apa, canal si salubritate</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="I50" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J50" s="6" t="n"/>
-      <c r="K50" s="6" t="n"/>
-      <c r="L50" s="6" t="n"/>
-      <c r="M50" s="6" t="n">
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="N51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '2,00 0,00' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>20.01.05</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>10,00 30,00 Carburanti si lubrifianti</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
-      <c r="I51" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J51" s="6" t="n"/>
-      <c r="K51" s="6" t="n"/>
-      <c r="L51" s="6" t="n"/>
-      <c r="M51" s="6" t="n">
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="N51" s="6" t="n">
+      <c r="N52" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="O52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '10,00 0,00' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>20.01.06</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>10,00 20,00 Piese de schimb</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
-      <c r="I52" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J52" s="6" t="n"/>
-      <c r="K52" s="6" t="n"/>
-      <c r="L52" s="6" t="n"/>
-      <c r="M52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '10,00 0,00' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>20.01.08</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>3,00 10,00 Posta, telecomunicatii, radio, tv, internet</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
-      <c r="I53" s="6" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J53" s="6" t="n"/>
-      <c r="K53" s="6" t="n"/>
-      <c r="L53" s="6" t="n"/>
-      <c r="M53" s="6" t="n">
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N53" s="6" t="n">
+      <c r="N54" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="O54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '4,00 0,00' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>20.01.09</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>15,00 50,00 Materiale si prestari de servicii cu caracter</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="6" t="n"/>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n"/>
-      <c r="K54" s="6" t="n"/>
-      <c r="L54" s="6" t="n"/>
-      <c r="M54" s="6" t="n">
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="N54" s="6" t="n">
+      <c r="N55" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="O55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "20,00 00'0" in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>20.01.30</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>20,00 60,00 Alte bunuri si servicii pentru intretinere si functional</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="6" t="n"/>
-      <c r="I55" s="6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J55" s="6" t="n"/>
-      <c r="K55" s="6" t="n"/>
-      <c r="L55" s="6" t="n"/>
-      <c r="M55" s="6" t="n">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="N55" s="6" t="n">
+      <c r="N56" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="O55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription); cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>20.03</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1,00 00'0 1,00 Hrana (cod 20.03.01+20.03.02) functionare</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>23</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="6" t="n"/>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n"/>
-      <c r="K56" s="6" t="n"/>
-      <c r="L56" s="6" t="n"/>
-      <c r="M56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="O56" s="4" t="n"/>
+      <c r="P56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="4" t="n"/>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2027; unparseable cell "00'0" in column est2026; unparseable cell '20,00 0,00' in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20.03.01</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1,00 1,00 1,00 1,00 Hrana pentru oameni</t>
+          <t>1,00 00'0 1,00 Hrana (cod 20.03.01+20.03.02) functionare</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -5443,86 +5474,86 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>20.03.01</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>1,00 1,00 1,00 1,00 Hrana pentru oameni</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n"/>
+      <c r="P58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '0,00 0,00' in column est2027; unparseable cell '0,00 0,00' in column est2026; unparseable cell '0,00 0,00' in column trim4; unparseable cell '0,00 0,00' in column trim3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>20.04</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>1,00 1,00 Medicamente si materiale sanitare (cod 2001 la 20.04.04)</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>23</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
-      <c r="I58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="n"/>
-      <c r="K58" s="6" t="n"/>
-      <c r="L58" s="6" t="n"/>
-      <c r="M58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription); cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>20,00 00'0 100,00 Bunuri de natura obiectelor de inventar (cod Medicamente 20.05.01+20.05.03+20.05.30)</t>
         </is>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n">
-        <v>80000</v>
-      </c>
+      <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N59" s="4" t="n"/>
-      <c r="O59" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n">
         <v>0</v>
       </c>
@@ -5536,171 +5567,162 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>unparseable cell "00'0" in column trim4</t>
+          <t>unparseable cell "00'0" in column est2027; unparseable cell "00'0 0,00" in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>20,00 00'0 100,00 Bunuri de natura obiectelor de inventar (cod Medicamente 20.05.01+20.05.03+20.05.30)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="4" t="n"/>
+      <c r="O60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column trim4; unparseable cell '80,00 0,00' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>20.05.01</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>10,00 0,00 50,00 Uniforme si echipament</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
-      <c r="I60" s="6" t="n"/>
-      <c r="J60" s="6" t="n"/>
-      <c r="K60" s="6" t="n"/>
-      <c r="L60" s="6" t="n"/>
-      <c r="M60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="4" t="n"/>
+      <c r="Q61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>20.05.30</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>10,00 50,00 Alte obiecte de inventar</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="6" t="n"/>
-      <c r="I61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="6" t="n"/>
-      <c r="K61" s="6" t="n"/>
-      <c r="L61" s="6" t="n"/>
-      <c r="M61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription); cell re-read from image (unverified transcription); cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>20.06</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>0,00 0,00 1,00 Deplasari, detasari, transferari (cod 20.06.01+20.06.02)</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>23</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="n"/>
-      <c r="H62" s="6" t="n"/>
-      <c r="I62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="6" t="n"/>
-      <c r="K62" s="6" t="n"/>
-      <c r="L62" s="6" t="n"/>
-      <c r="M62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
+      <c r="I62" s="4" t="n"/>
+      <c r="J62" s="4" t="n"/>
+      <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="4" t="n"/>
+      <c r="P62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="4" t="n"/>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2027; unparseable cell "00'0" in column est2026; unparseable cell '40,00 40,00 000' in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20.06.01</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0,00 00'0 1,00 Deplasari interne, detasari, transferari</t>
+          <t>0,00 0,00 1,00 Deplasari, detasari, transferari (cod 20.06.01+20.06.02)</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -5741,113 +5763,118 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>20.06.01</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>0,00 00'0 1,00 Deplasari interne, detasari, transferari</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="4" t="n"/>
+      <c r="Q64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell '0,00 0,00' in column est2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>15,00 0,00 20,00 Pregatire profesionala</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="n"/>
-      <c r="H64" s="6" t="n"/>
-      <c r="I64" s="6" t="n">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J64" s="6" t="n"/>
-      <c r="K64" s="6" t="n"/>
-      <c r="L64" s="6" t="n"/>
-      <c r="M64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription); cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Protectia muncii</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>24</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="I65" s="6" t="n"/>
-      <c r="J65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="L65" s="6" t="n"/>
-      <c r="M65" s="6" t="n"/>
-      <c r="N65" s="6" t="n"/>
-      <c r="O65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="6" t="n"/>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="J65" s="4" t="n"/>
+      <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="4" t="n"/>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2026; unparseable cell "00'0" in column trim3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alte cheltuieli (cod 20.30.01 la 20.30.04+20.30.06+20.30.07+20.30.09+20.30.3 0)</t>
+          <t>Protectia muncii</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -5860,14 +5887,14 @@
       </c>
       <c r="G66" s="6" t="n"/>
       <c r="H66" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I66" s="6" t="n"/>
       <c r="J66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>543</v>
+        <v>5</v>
       </c>
       <c r="L66" s="6" t="n"/>
       <c r="M66" s="6" t="n"/>
@@ -5881,73 +5908,73 @@
       <c r="Q66" s="6" t="n"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>20.30.03</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Prime de asigurare non-viata</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="n"/>
-      <c r="E67" s="7" t="n">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>20.30</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Alte cheltuieli (cod 20.30.01 la 20.30.04+20.30.06+20.30.07+20.30.09+20.30.3 0)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="I67" s="8" t="n"/>
-      <c r="J67" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" s="8" t="n"/>
-      <c r="M67" s="8" t="n"/>
-      <c r="N67" s="8" t="n"/>
-      <c r="O67" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="8" t="n"/>
-      <c r="R67" s="7" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="S67" s="7" t="inlineStr">
-        <is>
-          <t>duplicate of p21 with different values</t>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n">
+        <v>1122</v>
+      </c>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>543</v>
+      </c>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="4" t="n"/>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>20.30 trim1: parent 543,00 != sum(children) 45,00 (2 children); 20.30 total_2026: parent 1.122,00 != sum(children) 78,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>20.30.30</t>
+          <t>20.30.03</t>
         </is>
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>A heltuieli cu bunuri si servicii</t>
+          <t>Prime de asigurare non-viata</t>
         </is>
       </c>
       <c r="D68" s="7" t="n"/>
@@ -5961,14 +5988,14 @@
       </c>
       <c r="G68" s="8" t="n"/>
       <c r="H68" s="8" t="n">
-        <v>1110</v>
+        <v>12</v>
       </c>
       <c r="I68" s="8" t="n"/>
       <c r="J68" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>540</v>
+        <v>3</v>
       </c>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
@@ -5992,60 +6019,67 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>TITLUL XI ALTE CHELTUIELI (cod 59.01 + 59.02+59.08+59.11+59.12+59.15+59.17 +59.20+59.22+59.25+59.30+59.35)</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>20.30.30</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>A heltuieli cu bunuri si servicii</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="n"/>
+      <c r="E69" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I69" s="6" t="n"/>
-      <c r="J69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L69" s="6" t="n"/>
-      <c r="M69" s="6" t="n"/>
-      <c r="N69" s="6" t="n"/>
-      <c r="O69" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="P69" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q69" s="6" t="n"/>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n">
+        <v>1110</v>
+      </c>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="8" t="n">
+        <v>540</v>
+      </c>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
+      <c r="N69" s="8" t="n"/>
+      <c r="O69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="8" t="n"/>
+      <c r="R69" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="S69" s="7" t="inlineStr">
+        <is>
+          <t>duplicate of p21 with different values</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Burse</t>
+          <t>TITLUL XI ALTE CHELTUIELI (cod 59.01 + 59.02+59.08+59.11+59.12+59.15+59.17 +59.20+59.22+59.25+59.30+59.35)</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -6058,23 +6092,23 @@
       </c>
       <c r="G70" s="6" t="n"/>
       <c r="H70" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I70" s="6" t="n"/>
       <c r="J70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L70" s="6" t="n"/>
       <c r="M70" s="6" t="n"/>
       <c r="N70" s="6" t="n"/>
       <c r="O70" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q70" s="6" t="n"/>
       <c r="R70" t="inlineStr">
@@ -6086,12 +6120,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>59.40</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sume aferente persoanelor cu handicap neîncadrate</t>
+          <t>Burse</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -6104,14 +6138,14 @@
       </c>
       <c r="G71" s="6" t="n"/>
       <c r="H71" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I71" s="6" t="n"/>
       <c r="J71" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L71" s="6" t="n"/>
       <c r="M71" s="6" t="n"/>
@@ -6130,25 +6164,34 @@
       </c>
     </row>
     <row r="72">
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>SECTIUNEA DE DEZVOLTARE (cod 51+55+56+58+70+79+85)</t>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>59.40</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Sume aferente persoanelor cu handicap neîncadrate</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>24</v>
       </c>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
       <c r="G72" s="6" t="n"/>
       <c r="H72" s="6" t="n">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="I72" s="6" t="n"/>
       <c r="J72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="L72" s="6" t="n"/>
       <c r="M72" s="6" t="n"/>
@@ -6167,24 +6210,15 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>CHELTUIELI DE CAPITAL(cod 71+72+75)</t>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>SECTIUNEA DE DEZVOLTARE (cod 51+55+56+58+70+79+85)</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>24</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" s="6" t="n"/>
       <c r="H73" s="6" t="n">
         <v>400</v>
@@ -6215,12 +6249,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TITLUL XV ACTIVE NEFINANCIARE (cOd 71.01 +71.03)</t>
+          <t>CHELTUIELI DE CAPITAL(cod 71+72+75)</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -6261,12 +6295,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Active fixe (cod 71.01.01 la 71.01.03+71.01.30)</t>
+          <t>TITLUL XV ACTIVE NEFINANCIARE (cOd 71.01 +71.03)</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -6307,12 +6341,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>71.01.02</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Masini, echipamente si mijloace de transport</t>
+          <t>Active fixe (cod 71.01.01 la 71.01.03+71.01.30)</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -6345,6 +6379,52 @@
       </c>
       <c r="Q76" s="6" t="n"/>
       <c r="R76" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>71.01.02</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Masini, echipamente si mijloace de transport</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="n"/>
+      <c r="H77" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="I77" s="6" t="n"/>
+      <c r="J77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="L77" s="6" t="n"/>
+      <c r="M77" s="6" t="n"/>
+      <c r="N77" s="6" t="n"/>
+      <c r="O77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="6" t="n"/>
+      <c r="R77" t="inlineStr">
         <is>
           <t>ocr</t>
         </is>
@@ -6361,7 +6441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6407,250 +6487,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 10 total: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell '169,00 0,00' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 10 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell "0,00 00'0" in column trim1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 10 trim1: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell "0,00 00'0" in column trim2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 10.02 total: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell '210,00 0,00' in column trim3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 10.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell '210,00 0,00' in column trim4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20.30</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 20.30 total_2026: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (21%): "30,00 00'0 123,00 indicatorilor" vs 'Protectia muncii'</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>20.30</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 20.30 trim1: sum now consistent — applied</t>
+          <t>unparseable cell "00'0" in column est2027</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>est2027</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p3: 6 cells recovered</t>
+          <t>unparseable cell "00'0" in column est2027</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>est2028</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p23: 11 cells recovered</t>
+          <t>unparseable cell '00°0' in column est2028</t>
         </is>
       </c>
     </row>
@@ -6666,16 +6721,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>unparseable cell "0,00 00'0" in column trim1</t>
+          <t>unparseable cell "00'0" in column est2028</t>
         </is>
       </c>
     </row>
@@ -6691,41 +6746,41 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>unparseable cell "0,00 00'0" in column trim2</t>
+          <t>unparseable cell "00'0" in column est2028</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>20.14</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (21%): "30,00 00'0 123,00 indicatorilor" vs 'Protectia muncii'</t>
+          <t>unparseable cell "00'0" in column est2028</t>
         </is>
       </c>
     </row>
@@ -6745,34 +6800,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>unparseable cell "00'0" in column est2027</t>
+          <t>unparseable cell '15,00 0,00' in column trim4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>20.30</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>est2027</t>
@@ -6780,59 +6830,49 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '0,00 0,00' in column est2027</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>20.30.01</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '0,00 0,00' in column est2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>55.01.18</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>est2028</t>
@@ -6840,122 +6880,112 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '0,00 11.832,00' in column est2028</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>3</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>55.02</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell "00'0" in column est2027</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>info</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>est2028</t>
+        <v>16</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>10.03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>unparseable cell "00'0" in column est2028</t>
+          <t>rând absent, derivat aritmetic din formula părintelui 10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>est2028</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (30%): '(rând derivat din formula tipărită)' vs 'Contributii'</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>81.01</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>10.02 trim1: parent 365,00 != sum(children) 300,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -6975,24 +7005,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10 trim1: parent 3.373,00 != sum(children) 3.307,00 (2 children)</t>
+          <t>10.02 total: parent 1.195,00 != sum(children) 1.130,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -7001,28 +7031,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>23</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>credite_stinse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10 total_2026: parent 3.167,00 != sum(children) 3.102,00 (2 children)</t>
+          <t>unparseable cell 'Trim.1' in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -7031,28 +7056,23 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+        <v>23</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>credite_stinse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10 total: parent 10.900,00 != sum(children) 10.659,00 (2 children)</t>
+          <t>unparseable cell '6,00 726,00' in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -7061,28 +7081,23 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
+        <v>23</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>credite_stinse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10.02 trim1: parent 365,00 != sum(children) 300,00 (2 children)</t>
+          <t>unparseable cell '3,00 0,00' in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -7091,21 +7106,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
+        <v>23</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>credite_stinse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10.02 total: parent 1.195,00 != sum(children) 1.130,00 (2 children)</t>
+          <t>unparseable cell '3,00 0,00' in column credite_stinse</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7140,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>unparseable cell 'Trim.1' in column credite_stinse</t>
+          <t>unparseable cell '20,00 0,00' in column credite_stinse</t>
         </is>
       </c>
     </row>
@@ -7155,29 +7165,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>unparseable cell '6,00 726,00' in column credite_stinse</t>
+          <t>unparseable cell '2,00 0,00' in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>23</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>20.01.09</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>credite_stinse</t>
@@ -7185,127 +7190,107 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '10,00 0,00' in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>23</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>20.01.30</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>credite_stinse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '10,00 0,00' in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>23</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>20.01.30</t>
-        </is>
-      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>credite_stinse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '4,00 0,00' in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>23</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>credite_stinse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell "20,00 00'0" in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>23</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>credite_stinse</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell "00'0" in column est2027</t>
         </is>
       </c>
     </row>
@@ -7325,64 +7310,54 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>unparseable cell "00'0" in column trim4</t>
+          <t>unparseable cell "00'0" in column est2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>23</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>20.05.01</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>credite_stinse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '20,00 0,00' in column credite_stinse</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>23</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>20.05.30</t>
-        </is>
-      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>est2027</t>
@@ -7390,29 +7365,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '0,00 0,00' in column est2027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>23</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>20.05.30</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>est2026</t>
@@ -7420,97 +7390,82 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '0,00 0,00' in column est2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>23</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>20.05.30</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>credite_stinse</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '0,00 0,00' in column trim4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>23</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '0,00 0,00' in column trim3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>23</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell "00'0" in column est2027</t>
         </is>
       </c>
     </row>
@@ -7520,22 +7475,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>20.30.03</t>
+        <v>23</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>credite_stinse</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>duplicate of p21 with different values</t>
+          <t>unparseable cell "00'0 0,00" in column credite_stinse</t>
         </is>
       </c>
     </row>
@@ -7545,20 +7500,330 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>23</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>trim4</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column trim4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>23</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>credite_stinse</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>unparseable cell '80,00 0,00' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>23</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>est2028</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>23</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>est2027</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>23</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>est2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>23</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>credite_stinse</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>unparseable cell '40,00 40,00 000' in column credite_stinse</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>23</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>est2028</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>unparseable cell '0,00 0,00' in column est2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>23</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>est2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column est2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>23</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>trim3</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>unparseable cell "00'0" in column trim3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>24</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>20.30</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>trim1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>20.30 trim1: parent 543,00 != sum(children) 45,00 (2 children)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>24</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>20.30</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>20.30 total_2026: parent 1.122,00 != sum(children) 78,00 (2 children)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>warning</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C53" t="n">
         <v>24</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>20.30.03</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>duplicate of p21 with different values</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>24</v>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>20.30.30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>duplicate of p21 with different values</t>
         </is>
@@ -7575,7 +7840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7597,108 +7862,266 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>90</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>73</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.09999999999999</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>69.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>— BUGETUL PE TITLURI DE CHELTUIELI, ARTICOLE SI ALINEATE, PE A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>local, pag. 1-12, 44 linii</t>
-        </is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>458</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>— BUGETUL PE TITLURI DE CHELTUIELI, ARTICOLE SI ALINEATE, PEAN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>local, pag. 13-13, 8 linii</t>
-        </is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>326</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>71.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>c0a43dc0f559b98502643b3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5a1b9243adee0dc04fea7dcbb12b1c7768541d9e64a7da9f64956c2e843e8c4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>— BUGETUL PE TITLURI DE CHELTUIELI, ARTICOLE SI ALINEATE, PE A</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>local, pag. 14-24, 75 linii</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>local, pag. 1-12, 44 linii</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>— BUGETUL PE TITLURI DE CHELTUIELI, ARTICOLE SI ALINEATE, PEAN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>local, pag. 13-13, 8 linii</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>— BUGETUL PE TITLURI DE CHELTUIELI, ARTICOLE SI ALINEATE, PE A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>local, pag. 14-24, 76 linii</t>
         </is>
       </c>
     </row>
